--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -773,7 +773,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Beta: share sensitivity to ln(relative price)</t>
+          <t>Switch rate: Airbnb-hotel switching per % price gap</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
@@ -2654,7 +2654,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Values computed by analysis/src/choice_nights_driver.py (same model); rows = beta, columns = Airbnb ADR growth minus hotel ADR growth per year. Static output, not formulas.</t>
+          <t>Values computed by analysis/src/choice_nights_driver.py (same model); rows = switch rate (share sensitivity to the % price gap; called beta in the F&amp;F paper), columns = Airbnb ADR growth minus hotel ADR growth per year. Static output, not formulas.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2672,7 +2672,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>beta \ ADR premium</t>
+          <t>switch rate \ ADR premium</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calibration_2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Projection" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Countries" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Global" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration_2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projection" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Countries" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>-0.01</v>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>1.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>0.02</v>
@@ -1000,7 +1000,7 @@
         <v>2.5</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>0.04</v>
@@ -1012,7 +1012,7 @@
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Sources: booking share = fitted party-size distribution (research/party_size_distribution.md; anchors: guest arrivals ÷ bookings 2.97, Airbnb '&gt;80% of bookings are group trips'). Relative stay length: solo = 24% of nights ÷ 16% of bookings (Airbnb 2022); others from Inside Airbnb booked-run lengths by capacity. Hotel leisure party share = mean of Hawaii DBEDT 2024 hotel-only (Table 43) and Las Vegas Visitor Profile 2024. Relative nights: Portuguese ledger (solo 2.5 vs 3.6). Rooms per party: 2 people/room, families with small kids 1.5. Price ratio: party_size_cost_crossover.csv (Inside Airbnb Jun-2026 medians +14% fee vs rooms × $158.67 ADR). Mix drift: Airbnb family nights +15% vs total +8–10% (Airbnb Oct 2024); bedroom nights +12% vs nights +10% (Q2 2026).</t>
+          <t>Sources: booking share = fitted party-size distribution (research/party_size_distribution.md; anchors: guest arrivals ÷ bookings 2.97, Airbnb '&gt;80% of bookings are group trips'). Relative stay length: solo = 24% of nights ÷ 16% of bookings (Airbnb 2022); others from Inside Airbnb booked-run lengths by capacity. Hotel leisure party share = mean of Hawaii DBEDT 2024 hotel-only (Table 43) and Las Vegas Visitor Profile 2024. Relative nights: Portuguese ledger (solo 2.5 vs 3.6). Rooms per party: 2 people/room, families with small kids 1.5. Price ratio: party_size_cost_crossover.csv - the Jun-2026 Inside Airbnb `price` is a stay quote that ALREADY includes the guest service fee and amortised cleaning, so no fee is added (corrected 7 Sep 2026; the earlier 0.69/1.22/0.80/0.79 counted the 14% fee twice) vs rooms × $158.67 ADR. Descriptive - no formula reads this column. Mix drift: Airbnb family nights +15% vs total +8–10% (Airbnb Oct 2024); bedroom nights +12% vs nights +10% (Q2 2026).</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -2475,7 +2475,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Take rate — team input</t>
+          <t>Take rate — team input (carries the host-only fee migration)</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
@@ -2485,20 +2485,20 @@
         <v>0.134</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>FY2025 revenue ÷ GBV = 13.4% (Q4'25 shareholder letter)</t>
+          <t>FY2025 revenue ÷ GBV = 13.4% (Q4'25 letter). Steps to 13.6% by FY27: the single 15.5% host fee is ~+58bp on guest spend (~half of listings migrated by 2Q26, all by year end); FY26 is held at 13.4% because incentives for Services/Experiences/hotels are contra-revenue and management guided FY26 flat. Without the migration this line would drift to 12.9-13.1%.</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>How to wire it: replace the U.S./North-America nights growth plug in the team model with row 30 (or its growth in row 31). Keep ADR, take rate and FX where they are — this sheet only explains NIGHTS. For other regions, either repeat the calibration with that region's hotel data or apply the rest-of-world growth input.</t>
+          <t>How to wire it: replace the U.S./North-America nights growth plug in the team model with row 30 (or its growth in row 31). Keep ADR and FX where they are — this sheet only explains NIGHTS. The take-rate row is NOT a constant: it steps 13.4% → 13.6% by FY27 for the host-only fee migration, so reconcile it with the team model rather than overwriting it blind. For other regions, either repeat the calibration with that region's hotel data or apply the rest-of-world growth input.</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration_2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projection" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Countries" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Calibration_2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Projection" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Countries" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Global" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1189,37 +1189,68 @@
       <c r="I30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Stay length, nights per booking (NA)</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>EXPLICIT LEVER added 8 Sep 2026. FY20-25 10-Ks: NA 4.4/4.3/4.2/4.1/4.1/4.1 - FLAT since 2023, so the U.S. base carries no drag. Global fell 4.1-&gt;3.7 (-2.0%/yr, ~58mm nights forgone in 2025) but that is EMEA (4.4-&gt;3.8) and LatAm (4.4-&gt;3.6); APAC rose 2.8-&gt;3.3. Bear = the EMEA pattern reaches NA (-2%/yr -&gt; 2030 nights 154.8mm, CAGR +1.3%); bull = +1%/yr (179.8mm, +4.4%). Caveat: the 2020-22 plateau was COVID long-stay inflation, so part of the global fall is self-limiting normalisation</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Own-category nights growth (category adoption)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>0.04</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D32" s="7" t="n">
         <v>0.04</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E32" s="7" t="n">
         <v>0.035</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F32" s="7" t="n">
         <v>0.035</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G32" s="7" t="n">
         <v>0.03</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>GROUNDED: inverting the model on disclosed NA nights (146/154/158mm FY23-25) implies own-category growth 7.9% (2024) -&gt; 4.5% (2025); 4% entry = observed 2025 exit rate, fade extends the observed deceleration. category_adoption_evidence.csv</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1737,23 +1768,23 @@
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>B8*(1+Inputs!$H$20)*(1+Inputs!C31)</f>
+        <f>B8*(1+Inputs!$H$20)*(1+Inputs!C32)</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>C8*(1+Inputs!$H$20)*(1+Inputs!D31)</f>
+        <f>C8*(1+Inputs!$H$20)*(1+Inputs!D32)</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>D8*(1+Inputs!$H$20)*(1+Inputs!E31)</f>
+        <f>D8*(1+Inputs!$H$20)*(1+Inputs!E32)</f>
         <v/>
       </c>
       <c r="F8" s="15">
-        <f>E8*(1+Inputs!$H$20)*(1+Inputs!F31)</f>
+        <f>E8*(1+Inputs!$H$20)*(1+Inputs!F32)</f>
         <v/>
       </c>
       <c r="G8" s="15">
-        <f>F8*(1+Inputs!$H$20)*(1+Inputs!G31)</f>
+        <f>F8*(1+Inputs!$H$20)*(1+Inputs!G32)</f>
         <v/>
       </c>
       <c r="H8" s="2" t="n"/>
@@ -1889,23 +1920,23 @@
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>B14*(1+Inputs!$H$21)*(1+Inputs!C31)</f>
+        <f>B14*(1+Inputs!$H$21)*(1+Inputs!C32)</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>C14*(1+Inputs!$H$21)*(1+Inputs!D31)</f>
+        <f>C14*(1+Inputs!$H$21)*(1+Inputs!D32)</f>
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>D14*(1+Inputs!$H$21)*(1+Inputs!E31)</f>
+        <f>D14*(1+Inputs!$H$21)*(1+Inputs!E32)</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>E14*(1+Inputs!$H$21)*(1+Inputs!F31)</f>
+        <f>E14*(1+Inputs!$H$21)*(1+Inputs!F32)</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>F14*(1+Inputs!$H$21)*(1+Inputs!G31)</f>
+        <f>F14*(1+Inputs!$H$21)*(1+Inputs!G32)</f>
         <v/>
       </c>
       <c r="H14" s="2" t="n"/>
@@ -2041,23 +2072,23 @@
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>B20*(1+Inputs!$H$22)*(1+Inputs!C31)</f>
+        <f>B20*(1+Inputs!$H$22)*(1+Inputs!C32)</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>C20*(1+Inputs!$H$22)*(1+Inputs!D31)</f>
+        <f>C20*(1+Inputs!$H$22)*(1+Inputs!D32)</f>
         <v/>
       </c>
       <c r="E20" s="15">
-        <f>D20*(1+Inputs!$H$22)*(1+Inputs!E31)</f>
+        <f>D20*(1+Inputs!$H$22)*(1+Inputs!E32)</f>
         <v/>
       </c>
       <c r="F20" s="15">
-        <f>E20*(1+Inputs!$H$22)*(1+Inputs!F31)</f>
+        <f>E20*(1+Inputs!$H$22)*(1+Inputs!F32)</f>
         <v/>
       </c>
       <c r="G20" s="15">
-        <f>F20*(1+Inputs!$H$22)*(1+Inputs!G31)</f>
+        <f>F20*(1+Inputs!$H$22)*(1+Inputs!G32)</f>
         <v/>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -2193,23 +2224,23 @@
         <v/>
       </c>
       <c r="C26" s="15">
-        <f>B26*(1+Inputs!$H$23)*(1+Inputs!C31)</f>
+        <f>B26*(1+Inputs!$H$23)*(1+Inputs!C32)</f>
         <v/>
       </c>
       <c r="D26" s="15">
-        <f>C26*(1+Inputs!$H$23)*(1+Inputs!D31)</f>
+        <f>C26*(1+Inputs!$H$23)*(1+Inputs!D32)</f>
         <v/>
       </c>
       <c r="E26" s="15">
-        <f>D26*(1+Inputs!$H$23)*(1+Inputs!E31)</f>
+        <f>D26*(1+Inputs!$H$23)*(1+Inputs!E32)</f>
         <v/>
       </c>
       <c r="F26" s="15">
-        <f>E26*(1+Inputs!$H$23)*(1+Inputs!F31)</f>
+        <f>E26*(1+Inputs!$H$23)*(1+Inputs!F32)</f>
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>F26*(1+Inputs!$H$23)*(1+Inputs!G31)</f>
+        <f>F26*(1+Inputs!$H$23)*(1+Inputs!G32)</f>
         <v/>
       </c>
       <c r="H26" s="2" t="n"/>
@@ -3677,7 +3708,7 @@
         <v>13.1</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>224.2</v>
+        <v>221.8</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>104.4</v>
@@ -3686,10 +3717,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>570.9</v>
+        <v>568.6</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>0.0711</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="7">
@@ -3703,7 +3734,7 @@
         <v>13.4</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>237.2</v>
+        <v>232.8</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>119</v>
@@ -3712,10 +3743,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>611.8</v>
+        <v>607.4</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>0.0716</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="8">
@@ -3729,7 +3760,7 @@
         <v>13.9</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>250.2</v>
+        <v>243.6</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>133.3</v>
@@ -3738,10 +3769,10 @@
         <v>98.3</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>655.1</v>
+        <v>648.5</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>0.0708</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="9">
@@ -3755,7 +3786,7 @@
         <v>14.4</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>263.3</v>
+        <v>253.6</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>148</v>
@@ -3764,10 +3795,10 @@
         <v>108.2</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>699.1</v>
+        <v>689.4</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0.0672</v>
+        <v>0.0631</v>
       </c>
     </row>
     <row r="10">
@@ -3781,7 +3812,7 @@
         <v>14.9</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>276.2</v>
+        <v>263.8</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>162.8</v>
@@ -3790,10 +3821,10 @@
         <v>117.9</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>742.8</v>
+        <v>730.4</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="11">

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -530,6 +530,7 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -545,6 +546,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -556,6 +558,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -571,6 +574,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -592,6 +596,7 @@
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -613,6 +618,7 @@
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -634,6 +640,7 @@
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -655,6 +662,7 @@
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -670,6 +678,7 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -691,6 +700,7 @@
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -712,6 +722,7 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -733,6 +744,7 @@
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -754,6 +766,7 @@
       </c>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -769,6 +782,7 @@
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -790,6 +804,7 @@
       </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -811,6 +826,7 @@
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -822,6 +838,7 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -837,6 +854,7 @@
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -876,10 +894,15 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Mix drift / yr</t>
+          <t>Mix drift / yr — Airbnb pool</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Mix drift / yr — hotel pool</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>Product shift (logit pts/yr)</t>
         </is>
@@ -910,9 +933,12 @@
         <v>0.54</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I20" s="8" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="J20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,7 +969,10 @@
       <c r="H21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -972,9 +1001,12 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I22" s="8" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="J22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1003,16 +1035,19 @@
         <v>0.71</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I23" s="8" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="J23" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Sources: booking share = fitted party-size distribution (research/party_size_distribution.md; anchors: guest arrivals ÷ bookings 2.97, Airbnb '&gt;80% of bookings are group trips'). Relative stay length: solo = 24% of nights ÷ 16% of bookings (Airbnb 2022); others from Inside Airbnb booked-run lengths by capacity. Hotel leisure party share = mean of Hawaii DBEDT 2024 hotel-only (Table 43) and Las Vegas Visitor Profile 2024. Relative nights: Portuguese ledger (solo 2.5 vs 3.6). Rooms per party: 2 people/room, families with small kids 1.5. Price ratio: party_size_cost_crossover.csv - the Jun-2026 Inside Airbnb `price` is a stay quote that ALREADY includes the guest service fee and amortised cleaning, so no fee is added (corrected 7 Sep 2026; the earlier 0.69/1.22/0.80/0.79 counted the 14% fee twice) vs rooms × $158.67 ADR. Descriptive - no formula reads this column. Mix drift: Airbnb family nights +15% vs total +8–10% (Airbnb Oct 2024); bedroom nights +12% vs nights +10% (Q2 2026).</t>
+          <t>Sources: booking share = fitted party-size distribution (research/party_size_distribution.md; anchors: guest arrivals ÷ bookings 2.97, Airbnb '&gt;80% of bookings are group trips'). Relative stay length: solo = 24% of nights ÷ 16% of bookings (Airbnb 2022); others from Inside Airbnb booked-run lengths by capacity. Hotel leisure party share = mean of Hawaii DBEDT 2024 hotel-only (Table 43) and Las Vegas Visitor Profile 2024. Relative nights: Portuguese ledger (solo 2.5 vs 3.6). Rooms per party: 2 people/room, families with small kids 1.5. Price ratio: party_size_cost_crossover.csv - the Jun-2026 Inside Airbnb `price` is a stay quote that ALREADY includes the guest service fee and amortised cleaning, so no fee is added (corrected 7 Sep 2026; the earlier 0.69/1.22/0.80/0.79 counted the 14% fee twice) vs rooms × $158.67 ADR. Descriptive - no formula reads this column. Mix drift SPLIT 8 Sep 2026 into two vectors (was one applied to both pools). Airbnb pool implies mean party size +0.62%/yr, from the Inside Airbnb review-text proxy (74m reviews, 123 markets, 2018-25); hotel pool +0.26%/yr, from the Hawaii DBEDT ratio (rental 2.28-&gt;2.49 = +0.80%/yr vs hotel 2.22-&gt;2.30 = +0.34%/yr, 2013-24 - the only source observing both in one market). The old single vector implied +0.98%/yr for both and flattered the forecast.</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1023,6 +1058,7 @@
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1034,6 +1070,7 @@
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1049,6 +1086,7 @@
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -1088,6 +1126,7 @@
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1121,6 +1160,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1154,6 +1194,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -1187,6 +1228,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -1218,6 +1260,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1251,10 +1294,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A24:J24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2732,16 +2776,16 @@
         <v>2.5</v>
       </c>
       <c r="B5" s="15" t="n">
-        <v>190.4</v>
+        <v>177.2</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>174.6</v>
+        <v>162.6</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>162.1</v>
+        <v>150.9</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>152.1</v>
+        <v>141.7</v>
       </c>
     </row>
     <row r="6">
@@ -2749,16 +2793,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>209.8</v>
+        <v>195.3</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>174.6</v>
+        <v>162.6</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>151.9</v>
+        <v>141.6</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>137.5</v>
+        <v>128.3</v>
       </c>
     </row>
     <row r="7">
@@ -2766,16 +2810,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>228.3</v>
+        <v>212.5</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>174.6</v>
+        <v>162.6</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>145.3</v>
+        <v>135.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>129.7</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="8">
@@ -2783,16 +2827,16 @@
         <v>10.3</v>
       </c>
       <c r="B8" s="15" t="n">
-        <v>265.4</v>
+        <v>247.3</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>174.6</v>
+        <v>162.6</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>136.6</v>
+        <v>127.4</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>121.7</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="9">
@@ -2818,16 +2862,16 @@
         <v>2.5</v>
       </c>
       <c r="B11" s="16" t="n">
-        <v>0.0555132283409334</v>
+        <v>0.0506437962169632</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.0373893434930827</v>
+        <v>0.0326546119415493</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>0.0220154014798299</v>
+        <v>0.0174400360114008</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0091193684802821</v>
+        <v>0.0047105999956662</v>
       </c>
     </row>
     <row r="12">
@@ -2835,16 +2879,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.0761601872292379</v>
+        <v>0.071205171340674</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>0.0373893434930827</v>
+        <v>0.0326546119415493</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>0.008890254422301199</v>
+        <v>0.004484722715448</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.0110593966692612</v>
+        <v>-0.0151450817813916</v>
       </c>
     </row>
     <row r="13">
@@ -2852,16 +2896,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="16" t="n">
-        <v>0.0944674857690217</v>
+        <v>0.08949519047016639</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.0373893434930827</v>
+        <v>0.0326546119415493</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.0001120350858816</v>
+        <v>-0.0043826078750797</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0225181727552535</v>
+        <v>-0.0263852879405821</v>
       </c>
     </row>
     <row r="14">
@@ -2869,16 +2913,16 @@
         <v>10.3</v>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.1279356558617046</v>
+        <v>0.1230692151814347</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.0373893434930827</v>
+        <v>0.0326546119415493</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.0123695392230761</v>
+        <v>-0.016431544352648</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0348304467975015</v>
+        <v>-0.0384332957400108</v>
       </c>
     </row>
   </sheetData>
@@ -3678,10 +3722,10 @@
         <v>2025</v>
       </c>
       <c r="B5" s="15" t="n">
-        <v>145.4</v>
+        <v>138.4</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>12.6</v>
+        <v>19.6</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>215</v>
@@ -3702,10 +3746,10 @@
         <v>2026</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>150.2</v>
+        <v>142.4</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>13.1</v>
+        <v>20.1</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>221.8</v>
@@ -3717,10 +3761,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>568.6</v>
+        <v>567.9</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>0.0668</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="7">
@@ -3728,10 +3772,10 @@
         <v>2027</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>153.6</v>
+        <v>145.1</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>13.4</v>
+        <v>20.5</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>232.8</v>
@@ -3743,10 +3787,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>607.4</v>
+        <v>606</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>0.0682</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3754,10 +3798,10 @@
         <v>2028</v>
       </c>
       <c r="B8" s="15" t="n">
-        <v>159.4</v>
+        <v>149.8</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>13.9</v>
+        <v>21.2</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>243.6</v>
@@ -3769,10 +3813,10 @@
         <v>98.3</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>648.5</v>
+        <v>646.2</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>0.0677</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="9">
@@ -3780,10 +3824,10 @@
         <v>2029</v>
       </c>
       <c r="B9" s="15" t="n">
-        <v>165.4</v>
+        <v>154.7</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>14.4</v>
+        <v>21.9</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>253.6</v>
@@ -3795,10 +3839,10 @@
         <v>108.2</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>689.4</v>
+        <v>686.2</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0.0631</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="10">
@@ -3806,10 +3850,10 @@
         <v>2030</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>171.1</v>
+        <v>159.3</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>14.9</v>
+        <v>22.5</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>263.8</v>
@@ -3821,10 +3865,10 @@
         <v>117.9</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>730.4</v>
+        <v>726.2</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>0.0595</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="11">

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -3624,7 +3624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3881,12 +3881,8 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
     </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Reconciliation: team model WS13 base has total nights FY26 +9.9%, FY27 +8.9%, FY28 +7.4%; this build runs +7.1% / +7.2% / +7.1%. The gap is almost entirely North America (team 2H26 NA +7-8% vs this model's US +3.3% for 2026) — the choice model says NA growth at that pace needs share gains or category adoption above the 2025 exit rate.</t>
-        </is>
-      </c>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
@@ -3895,9 +3891,262 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>BY AIRBNB REPORTING SEGMENT (mm nights)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>LatAm</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>158</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>215</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>533</v>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>606</v>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>171</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>243.6</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>646.2</v>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>148</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>686.4</v>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>263.8</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>726.3</v>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>CAGR 2025-30</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Confidence differs sharply by region. North America is the full segment choice model; EMEA is calibrated on measured Eurostat platform and hotel nights for FR/ES/IT/DE and scaled. LatAm and APAC are growth fades off disclosed 2025 rates with NO hotel-side data and no choice model - yet they are 30% of 2025 nights and 62% of the 2025-30 growth. That is the least evidenced part of the forecast and the first place to spend more research.</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Reconciliation: team model WS13 base has total nights FY26 +9.9%, FY27 +8.9%, FY28 +7.4%; this build runs +7.1% / +7.2% / +7.1%. The gap is almost entirely North America (team 2H26 NA +7-8% vs this model's US +3.3% for 2026) — the choice model says NA growth at that pace needs share gains or category adoption above the 2025 exit rate.</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="3">
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/nights_choice_driver.xlsx
+++ b/docs/nights_choice_driver.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Countries" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Global" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Validation" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +140,9 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -613,7 +617,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>U.S. = 39% of FY2025 revenue ($4.76B of $12.2B; 61% non-U.S. per 10-K) ÷ NA revenue $5.196B</t>
+          <t>U.S. = 39% of FY2025 revenue ($4.76B of $12.2B) ÷ NA revenue $5.196B. A REVENUE share used as a NIGHTS share — exact only if revenue per night matches in the U.S. vs Canada/Mexico. It does not, so the U.S. ADR premium below corrects it. Resulting level is now supply-side validated — see the Validation sheet</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
@@ -4151,4 +4155,341 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="96" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Independent checks on the model — what has been tested, and what survived</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Every row is a check run against data outside the model. 'Held' means the model's value survived; 'contested' means a credible source disagrees and the disagreement is unresolved.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>What was tested</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Model value</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Check gave</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>U.S. nights level (supply side)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>138.4mm</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>156 vs 87.3 n/listing</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>HELD</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Bottom-up from raw Inside Airbnb across 8 cities at a calibrated 50% review rate gives 156 nights per active listing vs 87.3 implied nationally. The +78% gap is supply MIX: at ~30% large-urban, the other 70% need only ~58 nights/yr, which is seasonal rural/vacation-home supply. bottom_up_nights_from_raw.py</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Airbnb review rate</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>n/a (input to the check)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>43-60%, centred 50%</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>984,203 Inside Airbnb reviews against 3,304,396 Eurostat MEASURED platform stays for Vienna/Berlin/Brussels/Prague/Madrid. Rules out both literature extremes (30%, 72%). review_rate_calibration.py</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>U.S. revenue reconciliation</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>US_ADR_PREMIUM 1.05</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$4.97bn vs $4.76bn at 1.00</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>CORRECTED</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>A revenue share was being used as a nights share. Setting the premium to 1.05 clears it and moves U.S. nights 145.4 -&gt; 138.4mm. Levels scale; growth is unaffected.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Switch rate anchor</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>5.0 (grid 2.5-10.3)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10.3 reproduces F&amp;F exactly</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>HELD</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>F&amp;F (AER 2022) Appendix Table E9: a uniform +1% on all hotel prices lifts Airbnb demand 3.76%. Discounted from 10.3 for tier-level, 10-city, 2014 scope. Note it is near-inert at the team's near-parity ADR path.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Substitution share</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CONTESTABLE 0.38</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>NYC ADR +4.7-6.3% observed</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>CONTESTED</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>The model predicted +4.0-6.5% hotel ADR from LL18 and the EJPE 2025 diff-in-diff measured +4.7-6.3%. BUT Airbnb's own economists (CRA, Dec-2024) read the same event as 'limited substitution to hotels'. The disagreement is whether NYC hotels were capacity-constrained. Do not present as uncontested.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Rooms per party</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1 / 1 / 1.5 / 2.5</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2.01 guests/room (Japan)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>HELD</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Implies leisure guests-per-occupied-room of 2.0-2.27. Japan gives 2.01 blended (JTA guest-nights / MHLW room stock x occupancy), and the industry double-occupancy factor for holiday hotels is 1.8-2.5. Was the top uncited input.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Mix drift (party size)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>+0.62%/yr Airbnb side</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>NA +0.66%/yr</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>HELD FOR NA ONLY</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>122 markets / 36 countries: North America +0.66%/yr with 52% of markets significant. But EMEA is FLAT (-0.01%), corroborated independently by Spain's INE microdata. The global +0.62% was really a North America number - do not carry it into EMEA or APAC.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Party-size divergence</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>rental drifts 2.35x hotel</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1 market for, 2 against</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>NOT ESTABLISHED</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Hawaii supports it over 11 years. Spain's INE microdata says the rental/hotel ratio is FLAT (t=+0.12) over 11 years and the UK gap narrowed 2022-24. The strongest dataset is one of the two against. Treat as the optimistic case.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Party-size LEVEL gap</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>rentals host larger parties</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1.13-1.55x, 4 sources</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>HELD</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Booking rectour24 39/40 countries (t=10.2), Spain INE 1.167x stable over 12 years, UK GBTS 1.5x on family share, Hawaii 1.08x. This is the solid half of the party-size story.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>